--- a/data/trans_orig/P64D1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P64D1_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>107087</t>
+          <t>114943</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89804</t>
+          <t>94182</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127642</t>
+          <t>134682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>102174</t>
+          <t>108427</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89071</t>
+          <t>94255</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116591</t>
+          <t>123941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>209262</t>
+          <t>223369</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>187238</t>
+          <t>198550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234918</t>
+          <t>250574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>243715</t>
+          <t>266726</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223160</t>
+          <t>246987</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260998</t>
+          <t>287487</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>210420</t>
+          <t>224673</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>196003</t>
+          <t>209159</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223523</t>
+          <t>238845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>454134</t>
+          <t>491400</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>428478</t>
+          <t>464195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>476158</t>
+          <t>516219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>350802</t>
+          <t>381669</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>350802</t>
+          <t>381669</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>350802</t>
+          <t>381669</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>312594</t>
+          <t>333100</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>312594</t>
+          <t>333100</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>312594</t>
+          <t>333100</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>663396</t>
+          <t>714769</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>663396</t>
+          <t>714769</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>663396</t>
+          <t>714769</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67196</t>
+          <t>72622</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52744</t>
+          <t>57996</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82775</t>
+          <t>88768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81154</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68515</t>
+          <t>76907</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93607</t>
+          <t>104020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>148351</t>
+          <t>163249</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128805</t>
+          <t>143204</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>169356</t>
+          <t>185201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>236143</t>
+          <t>248204</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>220564</t>
+          <t>232058</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250595</t>
+          <t>262830</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>170976</t>
+          <t>182853</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>158523</t>
+          <t>169459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183615</t>
+          <t>196572</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>407118</t>
+          <t>431056</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>386113</t>
+          <t>409104</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>426664</t>
+          <t>451101</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>75,9%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>303339</t>
+          <t>320826</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>303339</t>
+          <t>320826</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>303339</t>
+          <t>320826</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>252130</t>
+          <t>273479</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>252130</t>
+          <t>273479</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>252130</t>
+          <t>273479</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>555469</t>
+          <t>594305</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>555469</t>
+          <t>594305</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>555469</t>
+          <t>594305</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64615</t>
+          <t>73032</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17164</t>
+          <t>58484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138677</t>
+          <t>90328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36369</t>
+          <t>40548</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29382</t>
+          <t>32668</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44359</t>
+          <t>49132</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>100985</t>
+          <t>113580</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40843</t>
+          <t>95013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187821</t>
+          <t>131015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>424910</t>
+          <t>198378</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>350848</t>
+          <t>181082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472361</t>
+          <t>212926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36843</t>
+          <t>42422</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28853</t>
+          <t>33838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43830</t>
+          <t>50302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>461752</t>
+          <t>240800</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>374916</t>
+          <t>223365</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>521894</t>
+          <t>259367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>489525</t>
+          <t>271410</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>489525</t>
+          <t>271410</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>489525</t>
+          <t>271410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>562737</t>
+          <t>354380</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>562737</t>
+          <t>354380</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>562737</t>
+          <t>354380</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>131733</t>
+          <t>157441</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109647</t>
+          <t>133498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153141</t>
+          <t>181508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>170748</t>
+          <t>194498</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152673</t>
+          <t>176559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>188982</t>
+          <t>214625</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>302482</t>
+          <t>351939</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>276190</t>
+          <t>321123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>334419</t>
+          <t>382442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>427981</t>
+          <t>463325</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>406573</t>
+          <t>439258</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>450067</t>
+          <t>487268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>255704</t>
+          <t>284097</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>237470</t>
+          <t>263970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273779</t>
+          <t>302036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>683684</t>
+          <t>747422</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651747</t>
+          <t>716919</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>709976</t>
+          <t>778238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>559714</t>
+          <t>620766</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>559714</t>
+          <t>620766</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>559714</t>
+          <t>620766</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>426452</t>
+          <t>478595</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>426452</t>
+          <t>478595</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>426452</t>
+          <t>478595</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>986166</t>
+          <t>1099361</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>986166</t>
+          <t>1099361</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>986166</t>
+          <t>1099361</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>53217</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21796</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47411</t>
+          <t>73228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>174541</t>
+          <t>120480</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118306</t>
+          <t>106267</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>264133</t>
+          <t>135854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>206623</t>
+          <t>173697</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>144680</t>
+          <t>149415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>326513</t>
+          <t>197122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>207830</t>
+          <t>253668</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192501</t>
+          <t>233657</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>218116</t>
+          <t>267758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>198899</t>
+          <t>192496</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109307</t>
+          <t>177122</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>255134</t>
+          <t>206709</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>406729</t>
+          <t>446165</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286839</t>
+          <t>422740</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>468672</t>
+          <t>470447</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,9%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>306885</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>306885</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>306885</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>373440</t>
+          <t>312976</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>373440</t>
+          <t>312976</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>373440</t>
+          <t>312976</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>613352</t>
+          <t>619862</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>613352</t>
+          <t>619862</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>613352</t>
+          <t>619862</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>402714</t>
+          <t>471254</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>263757</t>
+          <t>430486</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>472345</t>
+          <t>515613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>564988</t>
+          <t>554579</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>502690</t>
+          <t>522548</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>709202</t>
+          <t>588116</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>967702</t>
+          <t>1025833</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>777293</t>
+          <t>973055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1120868</t>
+          <t>1082168</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1540578</t>
+          <t>1430302</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1470947</t>
+          <t>1385943</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1679535</t>
+          <t>1471070</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>872841</t>
+          <t>926542</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>728627</t>
+          <t>893005</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>935139</t>
+          <t>958573</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2413418</t>
+          <t>2356844</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2260252</t>
+          <t>2300509</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2603827</t>
+          <t>2409622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1943292</t>
+          <t>1901556</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1943292</t>
+          <t>1901556</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1943292</t>
+          <t>1901556</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1437829</t>
+          <t>1481121</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1437829</t>
+          <t>1481121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1437829</t>
+          <t>1481121</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3381120</t>
+          <t>3382677</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3381120</t>
+          <t>3382677</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3381120</t>
+          <t>3382677</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
